--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/334FL_15A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/334FL_15A.xlsx
@@ -10756,7 +10756,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10892,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10909,7 +10909,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
